--- a/data/omics_glucose_transporter.xlsx
+++ b/data/omics_glucose_transporter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A3D449-9ADD-3C4F-9F06-EEF4A375D446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE14273-18BE-FF4B-BC01-2F4799A2B18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33460" yWindow="1280" windowWidth="26880" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34480" yWindow="2360" windowWidth="26880" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="67">
   <si>
     <t>all_gene</t>
   </si>
@@ -208,22 +208,28 @@
     <t>YHR094C</t>
   </si>
   <si>
+    <t>YMR011W</t>
+  </si>
+  <si>
+    <t>YDR345C</t>
+  </si>
+  <si>
+    <t>YHR096C</t>
+  </si>
+  <si>
+    <t>YDR343C</t>
+  </si>
+  <si>
     <t>YDR342C</t>
   </si>
   <si>
-    <t>YDR345C</t>
-  </si>
-  <si>
-    <t>YDR343C</t>
-  </si>
-  <si>
     <t>YHR092C</t>
   </si>
   <si>
-    <t>YMR011W</t>
-  </si>
-  <si>
-    <t>YHR096C</t>
+    <t>molecular/cell</t>
+  </si>
+  <si>
+    <t>sum</t>
   </si>
 </sst>
 </file>
@@ -242,6 +248,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -285,21 +292,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,6 +313,1062 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$33:$BG$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="58"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.296512898860291</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89940475999523439</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0278727113101764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0299693657674367</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.88299490824718518</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2760990427504577</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.3027766337843723</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1339437804031034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.6893071574976668</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.66695080483979996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.47070257225200585</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.90192184766723704</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.72272984791515527</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.86773371087661211</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1600984848162623</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.93141604671355505</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.90340111029673575</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2893342586257566</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.5167862471396711</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1248031248642483</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.5754344452091957</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.2858483167139889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.1016400546475866</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.9059365739143002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.329993853674976</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.8751535372506192</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.5589709304821864</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.471866057620334</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.4986410967463444</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.79330927691501707</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.4089486168208001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.4145230556220139</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.3337703754103352</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.9714454944771393</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.8406883054383565</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.3758363496149659</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.5732344721802876</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.0462829278647221</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.5768403831314102</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.3105700807656917</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.5067509105961365</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.4897379999697071</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.7937356165898906</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.3254454032294181</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0232296871222231</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0333216786502921</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.4664556269819577</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2.3203115781625523</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C916-1A4F-B3FD-22562EF9854A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2055929360"/>
+        <c:axId val="2055931008"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2055929360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2055931008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2055931008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2055929360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-SE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>66</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{728F6240-6530-6F46-93C0-20153C76F74A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -602,16 +1656,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BG33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="56" max="56" width="26.6640625" customWidth="1"/>
-    <col min="57" max="57" width="30.1640625" customWidth="1"/>
-    <col min="58" max="58" width="26.1640625" customWidth="1"/>
-    <col min="59" max="59" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="55" max="55" width="15.6640625" customWidth="1"/>
+    <col min="56" max="56" width="20" customWidth="1"/>
+    <col min="57" max="57" width="19" customWidth="1"/>
+    <col min="58" max="58" width="17.33203125" customWidth="1"/>
+    <col min="59" max="59" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:59" x14ac:dyDescent="0.2">
@@ -792,9 +1846,9 @@
     </row>
     <row r="2" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>805</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
@@ -818,35 +1872,161 @@
     </row>
     <row r="3" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>1378</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>1.3483734980710131E-5</v>
+        <v>5.8954486529802573E-7</v>
       </c>
       <c r="D3">
-        <v>4.1143590980346498E-7</v>
+        <v>2.4710445957913322E-7</v>
+      </c>
+      <c r="E3">
+        <v>4.3276342859999998E-7</v>
+      </c>
+      <c r="F3">
+        <v>4.4045034939999998E-7</v>
+      </c>
+      <c r="G3">
+        <v>4.7416226940000012E-7</v>
+      </c>
+      <c r="H3">
+        <v>1.0608224470000001E-6</v>
+      </c>
+      <c r="I3">
+        <v>1.005855408E-6</v>
+      </c>
+      <c r="J3">
+        <v>9.3223107890000016E-7</v>
+      </c>
+      <c r="K3">
+        <v>2.2580678200000001E-7</v>
+      </c>
+      <c r="L3">
+        <v>2.3540033430000001E-7</v>
+      </c>
+      <c r="M3">
+        <v>1.4785459600000001E-7</v>
+      </c>
+      <c r="N3">
+        <v>2.3488574170000001E-7</v>
+      </c>
+      <c r="O3">
+        <v>1.8326660040000001E-7</v>
+      </c>
+      <c r="P3">
+        <v>2.035534331E-7</v>
+      </c>
+      <c r="Q3">
+        <v>3.1665220720000002E-7</v>
+      </c>
+      <c r="R3">
+        <v>3.0459936710000002E-7</v>
+      </c>
+      <c r="S3">
+        <v>3.0887140069999997E-7</v>
+      </c>
+      <c r="T3">
+        <v>6.3034575910000007E-7</v>
+      </c>
+      <c r="U3">
+        <v>5.9212582269999997E-7</v>
+      </c>
+      <c r="V3">
+        <v>6.373034188000001E-7</v>
+      </c>
+      <c r="W3">
+        <v>6.216690567000001E-7</v>
+      </c>
+      <c r="X3">
+        <v>6.5781721170000004E-7</v>
+      </c>
+      <c r="Y3">
+        <v>7.7145614730000001E-7</v>
+      </c>
+      <c r="Z3">
+        <v>1.3860024820000001E-6</v>
+      </c>
+      <c r="AA3">
+        <v>1.543738884E-6</v>
+      </c>
+      <c r="AB3">
+        <v>1.3990053390000001E-6</v>
+      </c>
+      <c r="AC3">
+        <v>7.9495963740000011E-7</v>
+      </c>
+      <c r="AD3">
+        <v>4.0523372739999998E-7</v>
+      </c>
+      <c r="AE3">
+        <v>4.5511167810000002E-7</v>
+      </c>
+      <c r="AF3">
+        <v>1.038624921E-7</v>
+      </c>
+      <c r="AG3">
+        <v>2.4321818670000001E-7</v>
+      </c>
+      <c r="AH3">
+        <v>2.7075042559999999E-7</v>
+      </c>
+      <c r="AI3">
+        <v>5.736664553000001E-7</v>
+      </c>
+      <c r="AJ3">
+        <v>7.3536024799999999E-7</v>
+      </c>
+      <c r="AK3">
+        <v>6.6499399400000012E-7</v>
+      </c>
+      <c r="AL3">
+        <v>2.8752645610000001E-7</v>
+      </c>
+      <c r="AM3">
+        <v>2.8327725890000002E-7</v>
+      </c>
+      <c r="AN3">
+        <v>3.3453202389999998E-7</v>
+      </c>
+      <c r="AO3">
+        <v>4.0727738159999998E-7</v>
+      </c>
+      <c r="AP3">
+        <v>6.8830596170000006E-7</v>
+      </c>
+      <c r="AQ3">
+        <v>4.2080498149999997E-7</v>
+      </c>
+      <c r="AR3">
+        <v>3.7839319560000011E-7</v>
+      </c>
+      <c r="AS3">
+        <v>4.3640922250000001E-7</v>
+      </c>
+      <c r="AT3">
+        <v>3.609290115E-7</v>
       </c>
       <c r="BD3">
-        <v>4.7850557006834332E-7</v>
+        <v>6.7040912465660155E-7</v>
       </c>
       <c r="BE3">
-        <v>1.1686351161363869E-6</v>
+        <v>1.1143345885080171E-6</v>
       </c>
       <c r="BF3">
-        <v>8.3265958279510455E-6</v>
+        <v>1.0469258616134259E-6</v>
       </c>
       <c r="BG3">
-        <v>8.8841595504377284E-6</v>
+        <v>1.3142097733473401E-6</v>
       </c>
     </row>
     <row r="4" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1451</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
@@ -870,580 +2050,4115 @@
     </row>
     <row r="5" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>2098</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
       </c>
+      <c r="C5">
+        <v>1.5686487993651411E-6</v>
+      </c>
       <c r="D5">
-        <v>3.3136192478413309E-8</v>
-      </c>
-      <c r="E5">
-        <v>6.0213667210000004E-6</v>
-      </c>
-      <c r="F5">
-        <v>6.0268449330000007E-6</v>
-      </c>
-      <c r="G5">
-        <v>5.0702636080000014E-6</v>
-      </c>
-      <c r="H5">
-        <v>1.32310634E-5</v>
-      </c>
-      <c r="I5">
-        <v>1.3453542079999999E-5</v>
-      </c>
-      <c r="J5">
-        <v>1.246704564E-5</v>
-      </c>
-      <c r="K5">
-        <v>4.1024315870000002E-6</v>
-      </c>
-      <c r="L5">
-        <v>3.9524599429999999E-6</v>
-      </c>
-      <c r="M5">
-        <v>2.8077406149999999E-6</v>
-      </c>
-      <c r="N5">
-        <v>5.4283845499999996E-6</v>
-      </c>
-      <c r="O5">
-        <v>4.3548366589999986E-6</v>
-      </c>
-      <c r="P5">
-        <v>5.2450456430000011E-6</v>
-      </c>
-      <c r="Q5">
-        <v>6.9677386760000003E-6</v>
-      </c>
-      <c r="R5">
-        <v>5.5438683690000003E-6</v>
-      </c>
-      <c r="S5">
-        <v>5.3636873500000009E-6</v>
-      </c>
-      <c r="T5">
-        <v>1.374464552E-5</v>
-      </c>
-      <c r="U5">
-        <v>1.521106247E-5</v>
-      </c>
-      <c r="V5">
-        <v>1.270457808E-5</v>
-      </c>
-      <c r="W5">
-        <v>1.5549777969999998E-5</v>
-      </c>
-      <c r="X5">
-        <v>1.3695285440000001E-5</v>
-      </c>
-      <c r="Y5">
-        <v>1.8704095999999998E-5</v>
-      </c>
-      <c r="Z5">
-        <v>2.3139819370000001E-5</v>
-      </c>
-      <c r="AA5">
-        <v>2.5644787059999999E-5</v>
-      </c>
-      <c r="AB5">
-        <v>2.2933526309999999E-5</v>
-      </c>
-      <c r="AC5">
-        <v>1.52731111E-5</v>
-      </c>
-      <c r="AD5">
-        <v>8.8367813530000011E-6</v>
-      </c>
-      <c r="AE5">
-        <v>8.9550269310000002E-6</v>
-      </c>
-      <c r="AF5">
-        <v>4.8774170629999998E-6</v>
-      </c>
-      <c r="AG5">
-        <v>8.6037310970000008E-6</v>
-      </c>
-      <c r="AH5">
-        <v>8.6112013960000011E-6</v>
-      </c>
-      <c r="AI5">
-        <v>2.6638572700000001E-5</v>
-      </c>
-      <c r="AJ5">
-        <v>3.048091381E-5</v>
-      </c>
-      <c r="AK5">
-        <v>2.9730240739999999E-5</v>
-      </c>
-      <c r="AL5">
-        <v>8.35150712E-6</v>
-      </c>
-      <c r="AM5">
-        <v>9.5952416740000011E-6</v>
-      </c>
-      <c r="AN5">
-        <v>1.2514312189999999E-5</v>
-      </c>
-      <c r="AO5">
-        <v>9.4938834780000003E-6</v>
-      </c>
-      <c r="AP5">
-        <v>1.3820027470000001E-5</v>
-      </c>
-      <c r="AQ5">
-        <v>9.0402560750000005E-6</v>
-      </c>
-      <c r="AR5">
-        <v>8.9758418519999995E-6</v>
-      </c>
-      <c r="AS5">
-        <v>1.0826661579999999E-5</v>
-      </c>
-      <c r="AT5">
-        <v>7.9616940570000003E-6</v>
+        <v>2.7855729796182371E-8</v>
+      </c>
+      <c r="BD5">
+        <v>1.3496243744489711E-7</v>
+      </c>
+      <c r="BE5">
+        <v>1.3073807595928029E-7</v>
+      </c>
+      <c r="BF5">
+        <v>3.5452952359919557E-8</v>
+      </c>
+      <c r="BG5">
+        <v>3.689547219562916E-8</v>
       </c>
     </row>
     <row r="6" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2860</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B6" t="s">
         <v>62</v>
       </c>
-      <c r="C6">
-        <v>3.6197640053600299E-6</v>
-      </c>
       <c r="D6">
-        <v>1.8672104110839539E-6</v>
-      </c>
-      <c r="BD6">
-        <v>4.0504966153777098E-7</v>
-      </c>
-      <c r="BE6">
-        <v>5.2686926121118223E-7</v>
-      </c>
-      <c r="BF6">
-        <v>7.4805248900087552E-7</v>
-      </c>
-      <c r="BG6">
-        <v>6.6203299183853562E-7</v>
+        <v>3.3136192478413309E-8</v>
+      </c>
+      <c r="E6">
+        <v>6.0213667210000004E-6</v>
+      </c>
+      <c r="F6">
+        <v>6.0268449330000007E-6</v>
+      </c>
+      <c r="G6">
+        <v>5.0702636080000014E-6</v>
+      </c>
+      <c r="H6">
+        <v>1.32310634E-5</v>
+      </c>
+      <c r="I6">
+        <v>1.3453542079999999E-5</v>
+      </c>
+      <c r="J6">
+        <v>1.246704564E-5</v>
+      </c>
+      <c r="K6">
+        <v>4.1024315870000002E-6</v>
+      </c>
+      <c r="L6">
+        <v>3.9524599429999999E-6</v>
+      </c>
+      <c r="M6">
+        <v>2.8077406149999999E-6</v>
+      </c>
+      <c r="N6">
+        <v>5.4283845499999996E-6</v>
+      </c>
+      <c r="O6">
+        <v>4.3548366589999986E-6</v>
+      </c>
+      <c r="P6">
+        <v>5.2450456430000011E-6</v>
+      </c>
+      <c r="Q6">
+        <v>6.9677386760000003E-6</v>
+      </c>
+      <c r="R6">
+        <v>5.5438683690000003E-6</v>
+      </c>
+      <c r="S6">
+        <v>5.3636873500000009E-6</v>
+      </c>
+      <c r="T6">
+        <v>1.374464552E-5</v>
+      </c>
+      <c r="U6">
+        <v>1.521106247E-5</v>
+      </c>
+      <c r="V6">
+        <v>1.270457808E-5</v>
+      </c>
+      <c r="W6">
+        <v>1.5549777969999998E-5</v>
+      </c>
+      <c r="X6">
+        <v>1.3695285440000001E-5</v>
+      </c>
+      <c r="Y6">
+        <v>1.8704095999999998E-5</v>
+      </c>
+      <c r="Z6">
+        <v>2.3139819370000001E-5</v>
+      </c>
+      <c r="AA6">
+        <v>2.5644787059999999E-5</v>
+      </c>
+      <c r="AB6">
+        <v>2.2933526309999999E-5</v>
+      </c>
+      <c r="AC6">
+        <v>1.52731111E-5</v>
+      </c>
+      <c r="AD6">
+        <v>8.8367813530000011E-6</v>
+      </c>
+      <c r="AE6">
+        <v>8.9550269310000002E-6</v>
+      </c>
+      <c r="AF6">
+        <v>4.8774170629999998E-6</v>
+      </c>
+      <c r="AG6">
+        <v>8.6037310970000008E-6</v>
+      </c>
+      <c r="AH6">
+        <v>8.6112013960000011E-6</v>
+      </c>
+      <c r="AI6">
+        <v>2.6638572700000001E-5</v>
+      </c>
+      <c r="AJ6">
+        <v>3.048091381E-5</v>
+      </c>
+      <c r="AK6">
+        <v>2.9730240739999999E-5</v>
+      </c>
+      <c r="AL6">
+        <v>8.35150712E-6</v>
+      </c>
+      <c r="AM6">
+        <v>9.5952416740000011E-6</v>
+      </c>
+      <c r="AN6">
+        <v>1.2514312189999999E-5</v>
+      </c>
+      <c r="AO6">
+        <v>9.4938834780000003E-6</v>
+      </c>
+      <c r="AP6">
+        <v>1.3820027470000001E-5</v>
+      </c>
+      <c r="AQ6">
+        <v>9.0402560750000005E-6</v>
+      </c>
+      <c r="AR6">
+        <v>8.9758418519999995E-6</v>
+      </c>
+      <c r="AS6">
+        <v>1.0826661579999999E-5</v>
+      </c>
+      <c r="AT6">
+        <v>7.9616940570000003E-6</v>
       </c>
     </row>
     <row r="7" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>3888</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>3387</v>
+      </c>
+      <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7">
-        <v>5.8954486529802573E-7</v>
+        <v>1.3483734980710131E-5</v>
       </c>
       <c r="D7">
-        <v>2.4710445957913322E-7</v>
-      </c>
-      <c r="E7">
-        <v>4.3276342859999998E-7</v>
-      </c>
-      <c r="F7">
-        <v>4.4045034939999998E-7</v>
-      </c>
-      <c r="G7">
-        <v>4.7416226940000012E-7</v>
-      </c>
-      <c r="H7">
-        <v>1.0608224470000001E-6</v>
-      </c>
-      <c r="I7">
-        <v>1.005855408E-6</v>
-      </c>
-      <c r="J7">
-        <v>9.3223107890000016E-7</v>
-      </c>
-      <c r="K7">
-        <v>2.2580678200000001E-7</v>
-      </c>
-      <c r="L7">
-        <v>2.3540033430000001E-7</v>
-      </c>
-      <c r="M7">
-        <v>1.4785459600000001E-7</v>
-      </c>
-      <c r="N7">
-        <v>2.3488574170000001E-7</v>
-      </c>
-      <c r="O7">
-        <v>1.8326660040000001E-7</v>
-      </c>
-      <c r="P7">
-        <v>2.035534331E-7</v>
-      </c>
-      <c r="Q7">
-        <v>3.1665220720000002E-7</v>
-      </c>
-      <c r="R7">
-        <v>3.0459936710000002E-7</v>
-      </c>
-      <c r="S7">
-        <v>3.0887140069999997E-7</v>
-      </c>
-      <c r="T7">
-        <v>6.3034575910000007E-7</v>
-      </c>
-      <c r="U7">
-        <v>5.9212582269999997E-7</v>
-      </c>
-      <c r="V7">
-        <v>6.373034188000001E-7</v>
-      </c>
-      <c r="W7">
-        <v>6.216690567000001E-7</v>
-      </c>
-      <c r="X7">
-        <v>6.5781721170000004E-7</v>
-      </c>
-      <c r="Y7">
-        <v>7.7145614730000001E-7</v>
-      </c>
-      <c r="Z7">
-        <v>1.3860024820000001E-6</v>
-      </c>
-      <c r="AA7">
-        <v>1.543738884E-6</v>
-      </c>
-      <c r="AB7">
-        <v>1.3990053390000001E-6</v>
-      </c>
-      <c r="AC7">
-        <v>7.9495963740000011E-7</v>
-      </c>
-      <c r="AD7">
-        <v>4.0523372739999998E-7</v>
-      </c>
-      <c r="AE7">
-        <v>4.5511167810000002E-7</v>
-      </c>
-      <c r="AF7">
-        <v>1.038624921E-7</v>
-      </c>
-      <c r="AG7">
-        <v>2.4321818670000001E-7</v>
-      </c>
-      <c r="AH7">
-        <v>2.7075042559999999E-7</v>
-      </c>
-      <c r="AI7">
-        <v>5.736664553000001E-7</v>
-      </c>
-      <c r="AJ7">
-        <v>7.3536024799999999E-7</v>
-      </c>
-      <c r="AK7">
-        <v>6.6499399400000012E-7</v>
-      </c>
-      <c r="AL7">
-        <v>2.8752645610000001E-7</v>
-      </c>
-      <c r="AM7">
-        <v>2.8327725890000002E-7</v>
-      </c>
-      <c r="AN7">
-        <v>3.3453202389999998E-7</v>
-      </c>
-      <c r="AO7">
-        <v>4.0727738159999998E-7</v>
-      </c>
-      <c r="AP7">
-        <v>6.8830596170000006E-7</v>
-      </c>
-      <c r="AQ7">
-        <v>4.2080498149999997E-7</v>
-      </c>
-      <c r="AR7">
-        <v>3.7839319560000011E-7</v>
-      </c>
-      <c r="AS7">
-        <v>4.3640922250000001E-7</v>
-      </c>
-      <c r="AT7">
-        <v>3.609290115E-7</v>
+        <v>4.1143590980346498E-7</v>
       </c>
       <c r="BD7">
-        <v>6.7040912465660155E-7</v>
+        <v>4.7850557006834332E-7</v>
       </c>
       <c r="BE7">
-        <v>1.1143345885080171E-6</v>
+        <v>1.1686351161363869E-6</v>
       </c>
       <c r="BF7">
-        <v>1.0469258616134259E-6</v>
+        <v>8.3265958279510455E-6</v>
       </c>
       <c r="BG7">
-        <v>1.3142097733473401E-6</v>
+        <v>8.8841595504377284E-6</v>
       </c>
     </row>
     <row r="8" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>4137</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8">
-        <v>1.5686487993651411E-6</v>
+        <v>3.6197640053600299E-6</v>
       </c>
       <c r="D8">
-        <v>2.7855729796182371E-8</v>
+        <v>1.8672104110839539E-6</v>
       </c>
       <c r="BD8">
-        <v>1.3496243744489711E-7</v>
+        <v>4.0504966153777098E-7</v>
       </c>
       <c r="BE8">
-        <v>1.3073807595928029E-7</v>
+        <v>5.2686926121118223E-7</v>
       </c>
       <c r="BF8">
-        <v>3.5452952359919557E-8</v>
+        <v>7.4805248900087552E-7</v>
       </c>
       <c r="BG8">
-        <v>3.689547219562916E-8</v>
+        <v>6.6203299183853562E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
+    <row r="13" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="10" spans="1:59" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="4"/>
-      <c r="C10" s="3">
-        <f>SUM(C2:C8)</f>
-        <v>3.3257409416683908E-5</v>
-      </c>
-      <c r="D10" s="3">
-        <f>SUM(D2:D8)</f>
-        <v>5.6474652107261583E-6</v>
-      </c>
-      <c r="E10" s="3">
-        <f>SUM(E2:E8)</f>
-        <v>6.4541301496000006E-6</v>
-      </c>
-      <c r="F10" s="3">
-        <f>SUM(F2:F8)</f>
-        <v>6.4672952824000007E-6</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" ref="G10:BG10" si="0">SUM(G2:G8)</f>
-        <v>5.5444258774000015E-6</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4291885846999999E-5</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4459397487999999E-5</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.33992767189E-5</v>
-      </c>
-      <c r="K10" s="3">
-        <f t="shared" si="0"/>
-        <v>4.3282383690000001E-6</v>
-      </c>
-      <c r="L10" s="3">
-        <f t="shared" si="0"/>
-        <v>4.1878602772999996E-6</v>
-      </c>
-      <c r="M10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.9555952109999998E-6</v>
-      </c>
-      <c r="N10" s="3">
-        <f t="shared" si="0"/>
-        <v>5.6632702916999994E-6</v>
-      </c>
-      <c r="O10" s="3">
-        <f t="shared" si="0"/>
-        <v>4.5381032593999985E-6</v>
-      </c>
-      <c r="P10" s="3">
-        <f t="shared" si="0"/>
-        <v>5.448599076100001E-6</v>
-      </c>
-      <c r="Q10" s="3">
-        <f t="shared" si="0"/>
-        <v>7.2843908832000007E-6</v>
-      </c>
-      <c r="R10" s="3">
-        <f t="shared" si="0"/>
-        <v>5.8484677361000006E-6</v>
-      </c>
-      <c r="S10" s="3">
-        <f t="shared" si="0"/>
-        <v>5.6725587507000009E-6</v>
-      </c>
-      <c r="T10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.43749912791E-5</v>
-      </c>
-      <c r="U10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.5803188292699999E-5</v>
-      </c>
-      <c r="V10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.3341881498800001E-5</v>
-      </c>
-      <c r="W10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.6171447026699997E-5</v>
-      </c>
-      <c r="X10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4353102651700001E-5</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.9475552147299998E-5</v>
-      </c>
-      <c r="Z10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.4525821852000002E-5</v>
-      </c>
-      <c r="AA10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.7188525943999999E-5</v>
-      </c>
-      <c r="AB10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.4332531648999998E-5</v>
-      </c>
-      <c r="AC10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.60680707374E-5</v>
-      </c>
-      <c r="AD10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.2420150804000014E-6</v>
-      </c>
-      <c r="AE10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.4101386091000004E-6</v>
-      </c>
-      <c r="AF10" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9812795550999996E-6</v>
-      </c>
-      <c r="AG10" s="3">
-        <f t="shared" si="0"/>
-        <v>8.8469492837E-6</v>
-      </c>
-      <c r="AH10" s="3">
-        <f t="shared" si="0"/>
-        <v>8.8819518216000003E-6</v>
-      </c>
-      <c r="AI10" s="3">
-        <f t="shared" si="0"/>
-        <v>2.7212239155300001E-5</v>
-      </c>
-      <c r="AJ10" s="3">
-        <f t="shared" si="0"/>
-        <v>3.1216274058000002E-5</v>
-      </c>
-      <c r="AK10" s="3">
-        <f t="shared" si="0"/>
-        <v>3.0395234733999998E-5</v>
-      </c>
-      <c r="AL10" s="3">
-        <f t="shared" si="0"/>
-        <v>8.6390335760999995E-6</v>
-      </c>
-      <c r="AM10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.8785189329000005E-6</v>
-      </c>
-      <c r="AN10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.2848844213899999E-5</v>
-      </c>
-      <c r="AO10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.9011608596000006E-6</v>
-      </c>
-      <c r="AP10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4508333431700001E-5</v>
-      </c>
-      <c r="AQ10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.4610610565000011E-6</v>
-      </c>
-      <c r="AR10" s="3">
-        <f t="shared" si="0"/>
-        <v>9.3542350475999991E-6</v>
-      </c>
-      <c r="AS10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1263070802499999E-5</v>
-      </c>
-      <c r="AT10" s="3">
-        <f t="shared" si="0"/>
-        <v>8.3226230685000001E-6</v>
-      </c>
-      <c r="AU10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AV10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AW10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AX10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AY10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BA10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BB10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="3">
-        <f t="shared" si="0"/>
-        <v>6.4249760704352785E-6</v>
-      </c>
-      <c r="BE10" s="3">
-        <f t="shared" si="0"/>
-        <v>6.4883448378654365E-6</v>
-      </c>
-      <c r="BF10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.5487156580374547E-5</v>
-      </c>
-      <c r="BG10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4569501406449701E-5</v>
+    <row r="14" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>349</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15">
+        <f>C2*7829800000</f>
+        <v>35050.70843228772</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:BG19" si="0">D2*7829800000</f>
+        <v>3558.6841796742597</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <f t="shared" si="0"/>
+        <v>7750.0391568627165</v>
+      </c>
+      <c r="BE15">
+        <f t="shared" si="0"/>
+        <v>5811.9695978692534</v>
+      </c>
+      <c r="BF15">
+        <f t="shared" si="0"/>
+        <v>3397.9088836460937</v>
+      </c>
+      <c r="BG15">
+        <f t="shared" si="0"/>
+        <v>2011.8866425351227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>739</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:R21" si="1">C3*7829800000</f>
+        <v>4616.0183863104821</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>1934.7784976126973</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>3388.4510932522799</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>3448.6381457321199</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>3712.5957369481207</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>8306.0275955205998</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>7875.6466735583999</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>7299.182901571221</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>1768.0219417036001</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>1843.13753750214</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="1"/>
+        <v>1157.6719157608002</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>1839.10838036266</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="1"/>
+        <v>1434.9408278119201</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>1593.7826704863801</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="1"/>
+        <v>2479.3234519345601</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>2384.9521245195801</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>2418.40129320086</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="0"/>
+        <v>4935.4812246011807</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="0"/>
+        <v>4636.2267665764593</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="0"/>
+        <v>4989.9583085202412</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>4867.5443801496604</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="0"/>
+        <v>5150.5772041686605</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>6040.3473421295403</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="0"/>
+        <v>10852.122233563601</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="0"/>
+        <v>12087.166713943199</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="0"/>
+        <v>10953.932003302201</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="0"/>
+        <v>6224.3749689145207</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="0"/>
+        <v>3172.89903879652</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="0"/>
+        <v>3563.4334171873802</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="0"/>
+        <v>813.22254064458002</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="0"/>
+        <v>1904.34975822366</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="0"/>
+        <v>2119.9216823628799</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="0"/>
+        <v>4491.6936117079404</v>
+      </c>
+      <c r="AJ16">
+        <f t="shared" si="0"/>
+        <v>5757.7236697904</v>
+      </c>
+      <c r="AK16">
+        <f t="shared" si="0"/>
+        <v>5206.7699742212008</v>
+      </c>
+      <c r="AL16">
+        <f t="shared" si="0"/>
+        <v>2251.27464597178</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" si="0"/>
+        <v>2218.00428173522</v>
+      </c>
+      <c r="AN16">
+        <f t="shared" si="0"/>
+        <v>2619.31884073222</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="0"/>
+        <v>3188.9004424516797</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="0"/>
+        <v>5389.2980189186601</v>
+      </c>
+      <c r="AQ16">
+        <f t="shared" si="0"/>
+        <v>3294.8188441487</v>
+      </c>
+      <c r="AR16">
+        <f t="shared" si="0"/>
+        <v>2962.7430429088809</v>
+      </c>
+      <c r="AS16">
+        <f t="shared" si="0"/>
+        <v>3416.9969303305002</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="0"/>
+        <v>2826.0019742426998</v>
+      </c>
+      <c r="AU16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <f t="shared" si="0"/>
+        <v>5249.1693642362588</v>
+      </c>
+      <c r="BE16">
+        <f t="shared" si="0"/>
+        <v>8725.0169611000729</v>
+      </c>
+      <c r="BF16">
+        <f t="shared" si="0"/>
+        <v>8197.2201112608018</v>
+      </c>
+      <c r="BG16">
+        <f t="shared" si="0"/>
+        <v>10289.999683355003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>1295</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>74532.954701752184</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>20406.160913346779</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <f t="shared" si="0"/>
+        <v>29332.279470059566</v>
+      </c>
+      <c r="BE17">
+        <f t="shared" si="0"/>
+        <v>21966.342691647496</v>
+      </c>
+      <c r="BF17">
+        <f t="shared" si="0"/>
+        <v>38335.938679651852</v>
+      </c>
+      <c r="BG17">
+        <f t="shared" si="0"/>
+        <v>26740.733250617701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>2258</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>12282.206369269181</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>218.10479315814874</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <f t="shared" si="0"/>
+        <v>1056.7288927060554</v>
+      </c>
+      <c r="BE18">
+        <f t="shared" si="0"/>
+        <v>1023.6529871459728</v>
+      </c>
+      <c r="BF18">
+        <f t="shared" si="0"/>
+        <v>277.58952638769813</v>
+      </c>
+      <c r="BG18">
+        <f t="shared" si="0"/>
+        <v>288.8841681973372</v>
+      </c>
+    </row>
+    <row r="19" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>2557</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>259.44975986748051</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>47146.0971520858</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>47188.990456403408</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>39699.149997918408</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>103596.58020932</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>105338.543777984</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>97614.473952072003</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>32121.218839892601</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="0"/>
+        <v>30946.9708617014</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="0"/>
+        <v>21984.047467327</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="0"/>
+        <v>42503.165349589995</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>34097.500072638191</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="0"/>
+        <v>41067.658375561412</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>54556.000285344802</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="0"/>
+        <v>43407.380555596203</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="0"/>
+        <v>41996.599213030007</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="0"/>
+        <v>107617.82549249599</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="0"/>
+        <v>119099.576927606</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="0"/>
+        <v>99474.305450783999</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>121751.65154950599</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="0"/>
+        <v>107231.345938112</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="0"/>
+        <v>146449.33086079999</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="0"/>
+        <v>181180.157703226</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="0"/>
+        <v>200793.55372238799</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="0"/>
+        <v>179564.92430203798</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="0"/>
+        <v>119585.40529077999</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="0"/>
+        <v>69190.230637719404</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="0"/>
+        <v>70116.069864343808</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="0"/>
+        <v>38189.200119877401</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="0"/>
+        <v>67365.493743290601</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="0"/>
+        <v>67423.984690400815</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="0"/>
+        <v>208574.69652646</v>
+      </c>
+      <c r="AJ19">
+        <f t="shared" si="0"/>
+        <v>238659.45894953801</v>
+      </c>
+      <c r="AK19">
+        <f t="shared" si="0"/>
+        <v>232781.83894605198</v>
+      </c>
+      <c r="AL19">
+        <f t="shared" si="0"/>
+        <v>65390.630448176002</v>
+      </c>
+      <c r="AM19">
+        <f t="shared" si="0"/>
+        <v>75128.823259085213</v>
+      </c>
+      <c r="AN19">
+        <f t="shared" si="0"/>
+        <v>97984.561585261996</v>
+      </c>
+      <c r="AO19">
+        <f t="shared" si="0"/>
+        <v>74335.208856044395</v>
+      </c>
+      <c r="AP19">
+        <f t="shared" si="0"/>
+        <v>108208.05108460601</v>
+      </c>
+      <c r="AQ19">
+        <f t="shared" si="0"/>
+        <v>70783.397016035</v>
+      </c>
+      <c r="AR19">
+        <f t="shared" si="0"/>
+        <v>70279.046532789594</v>
+      </c>
+      <c r="AS19">
+        <f t="shared" si="0"/>
+        <v>84770.594839083991</v>
+      </c>
+      <c r="AT19">
+        <f t="shared" si="0"/>
+        <v>62338.4721274986</v>
+      </c>
+      <c r="AU19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <f t="shared" ref="D19:BG21" si="2">AX6*7829800000</f>
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>3387</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>105574.94815196418</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>3221.4608865791702</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <f t="shared" si="2"/>
+        <v>3746.6029125211144</v>
+      </c>
+      <c r="BE20">
+        <f t="shared" si="2"/>
+        <v>9150.1792323246827</v>
+      </c>
+      <c r="BF20">
+        <f t="shared" si="2"/>
+        <v>65195.580013691098</v>
+      </c>
+      <c r="BG20">
+        <f t="shared" si="2"/>
+        <v>69561.192448017333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>3855</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>28342.028209167962</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>14619.884076705142</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <f t="shared" si="2"/>
+        <v>3171.4578399084394</v>
+      </c>
+      <c r="BE21">
+        <f t="shared" si="2"/>
+        <v>4125.2809414313142</v>
+      </c>
+      <c r="BF21">
+        <f t="shared" si="2"/>
+        <v>5857.1013783790549</v>
+      </c>
+      <c r="BG21">
+        <f t="shared" si="2"/>
+        <v>5183.5859194973664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>349</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25">
+        <f>C15*20.34</f>
+        <v>712931.40951273218</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ref="D25:BG29" si="3">D15*20.34</f>
+        <v>72383.636214574435</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <f t="shared" si="3"/>
+        <v>157635.79645058766</v>
+      </c>
+      <c r="BE25">
+        <f t="shared" si="3"/>
+        <v>118215.46162066062</v>
+      </c>
+      <c r="BF25">
+        <f t="shared" si="3"/>
+        <v>69113.466693361552</v>
+      </c>
+      <c r="BG25">
+        <f t="shared" si="3"/>
+        <v>40921.774309164393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>739</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:R31" si="4">C16*20.34</f>
+        <v>93889.813977555212</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="4"/>
+        <v>39353.394641442261</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="4"/>
+        <v>68921.095236751367</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="4"/>
+        <v>70145.299884191321</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>75514.197289524775</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>168944.60129288901</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="4"/>
+        <v>160190.65334017784</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="4"/>
+        <v>148465.38021795862</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="4"/>
+        <v>35961.566294251228</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="4"/>
+        <v>37489.41751279353</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="4"/>
+        <v>23547.046766574676</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="4"/>
+        <v>37407.464456576505</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="4"/>
+        <v>29186.696437694456</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="4"/>
+        <v>32417.539517692971</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="4"/>
+        <v>50429.43901234895</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="4"/>
+        <v>48509.926212728256</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="3"/>
+        <v>49190.282303705491</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="3"/>
+        <v>100387.68810838801</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="3"/>
+        <v>94300.852432165178</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="3"/>
+        <v>101495.7519953017</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="3"/>
+        <v>99005.852692244094</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="3"/>
+        <v>104762.74033279055</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="3"/>
+        <v>122860.66493891485</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="3"/>
+        <v>220732.16623068365</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="3"/>
+        <v>245852.97096160467</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="3"/>
+        <v>222802.97694716678</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="3"/>
+        <v>126603.78686772136</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="3"/>
+        <v>64536.76644912122</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="3"/>
+        <v>72480.235705591316</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="3"/>
+        <v>16540.946476710757</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="3"/>
+        <v>38734.474082269247</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="3"/>
+        <v>43119.207019260975</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="3"/>
+        <v>91361.048062139511</v>
+      </c>
+      <c r="AJ26">
+        <f t="shared" si="3"/>
+        <v>117112.09944353673</v>
+      </c>
+      <c r="AK26">
+        <f t="shared" si="3"/>
+        <v>105905.70127565922</v>
+      </c>
+      <c r="AL26">
+        <f t="shared" si="3"/>
+        <v>45790.926299066006</v>
+      </c>
+      <c r="AM26">
+        <f t="shared" si="3"/>
+        <v>45114.207090494376</v>
+      </c>
+      <c r="AN26">
+        <f t="shared" si="3"/>
+        <v>53276.945220493355</v>
+      </c>
+      <c r="AO26">
+        <f t="shared" si="3"/>
+        <v>64862.234999467168</v>
+      </c>
+      <c r="AP26">
+        <f t="shared" si="3"/>
+        <v>109618.32170480555</v>
+      </c>
+      <c r="AQ26">
+        <f t="shared" si="3"/>
+        <v>67016.615289984562</v>
+      </c>
+      <c r="AR26">
+        <f t="shared" si="3"/>
+        <v>60262.193492766637</v>
+      </c>
+      <c r="AS26">
+        <f t="shared" si="3"/>
+        <v>69501.717562922378</v>
+      </c>
+      <c r="AT26">
+        <f t="shared" si="3"/>
+        <v>57480.880156096515</v>
+      </c>
+      <c r="AU26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <f t="shared" si="3"/>
+        <v>106768.1048685655</v>
+      </c>
+      <c r="BE26">
+        <f t="shared" si="3"/>
+        <v>177466.84498877547</v>
+      </c>
+      <c r="BF26">
+        <f t="shared" si="3"/>
+        <v>166731.45706304471</v>
+      </c>
+      <c r="BG26">
+        <f t="shared" si="3"/>
+        <v>209298.59355944075</v>
+      </c>
+    </row>
+    <row r="27" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>1295</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="4"/>
+        <v>1516000.2986336395</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="3"/>
+        <v>415061.31297747348</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <f t="shared" si="3"/>
+        <v>596618.5644210116</v>
+      </c>
+      <c r="BE27">
+        <f t="shared" si="3"/>
+        <v>446795.41034811008</v>
+      </c>
+      <c r="BF27">
+        <f t="shared" si="3"/>
+        <v>779752.99274411867</v>
+      </c>
+      <c r="BG27">
+        <f t="shared" si="3"/>
+        <v>543906.51431756408</v>
+      </c>
+    </row>
+    <row r="28" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>2258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="4"/>
+        <v>249820.07755093515</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="3"/>
+        <v>4436.2514928367455</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <f t="shared" si="3"/>
+        <v>21493.865677641166</v>
+      </c>
+      <c r="BE28">
+        <f t="shared" si="3"/>
+        <v>20821.101758549088</v>
+      </c>
+      <c r="BF28">
+        <f t="shared" si="3"/>
+        <v>5646.1709667257801</v>
+      </c>
+      <c r="BG28">
+        <f t="shared" si="3"/>
+        <v>5875.9039811338389</v>
+      </c>
+    </row>
+    <row r="29" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>2557</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="3"/>
+        <v>5277.2081157045532</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="3"/>
+        <v>958951.61607342516</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>959824.06588324532</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="3"/>
+        <v>807480.71095766046</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="3"/>
+        <v>2107154.4414575687</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>2142585.9804441947</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>1985478.4001851445</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="3"/>
+        <v>653345.59120341553</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="3"/>
+        <v>629461.38732700644</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="3"/>
+        <v>447155.52548543119</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="3"/>
+        <v>864514.38321066054</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="3"/>
+        <v>693543.15147746075</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="3"/>
+        <v>835316.17135891912</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="3"/>
+        <v>1109669.0458039134</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="3"/>
+        <v>882906.12050082674</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="3"/>
+        <v>854210.82799303031</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="3"/>
+        <v>2188946.5705173686</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="3"/>
+        <v>2422485.3947075061</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="3"/>
+        <v>2023307.3728689465</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="3"/>
+        <v>2476428.5925169517</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="3"/>
+        <v>2181085.5763811981</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="3"/>
+        <v>2978779.3897086717</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="3"/>
+        <v>3685204.4076836165</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="3"/>
+        <v>4084140.8827133719</v>
+      </c>
+      <c r="AB29">
+        <f t="shared" si="3"/>
+        <v>3652350.5603034524</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="3"/>
+        <v>2432367.1436144649</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="3"/>
+        <v>1407329.2911712127</v>
+      </c>
+      <c r="AE29">
+        <f t="shared" si="3"/>
+        <v>1426160.8610407531</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="3"/>
+        <v>776768.33043830632</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="3"/>
+        <v>1370214.1427385309</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="3"/>
+        <v>1371403.8486027527</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="3"/>
+        <v>4242409.3273481959</v>
+      </c>
+      <c r="AJ29">
+        <f t="shared" si="3"/>
+        <v>4854333.3950336026</v>
+      </c>
+      <c r="AK29">
+        <f t="shared" si="3"/>
+        <v>4734782.6041626977</v>
+      </c>
+      <c r="AL29">
+        <f t="shared" si="3"/>
+        <v>1330045.4233158999</v>
+      </c>
+      <c r="AM29">
+        <f t="shared" si="3"/>
+        <v>1528120.2650897931</v>
+      </c>
+      <c r="AN29">
+        <f t="shared" si="3"/>
+        <v>1993005.982644229</v>
+      </c>
+      <c r="AO29">
+        <f t="shared" si="3"/>
+        <v>1511978.1481319431</v>
+      </c>
+      <c r="AP29">
+        <f t="shared" si="3"/>
+        <v>2200951.7590608862</v>
+      </c>
+      <c r="AQ29">
+        <f t="shared" si="3"/>
+        <v>1439734.295306152</v>
+      </c>
+      <c r="AR29">
+        <f t="shared" si="3"/>
+        <v>1429475.8064769404</v>
+      </c>
+      <c r="AS29">
+        <f t="shared" si="3"/>
+        <v>1724233.8990269683</v>
+      </c>
+      <c r="AT29">
+        <f t="shared" si="3"/>
+        <v>1267964.5230733214</v>
+      </c>
+      <c r="AU29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <f t="shared" ref="D29:BG31" si="5">AX19*20.34</f>
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>3387</v>
+      </c>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="4"/>
+        <v>2147394.4454109515</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="5"/>
+        <v>65524.514433020318</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <f t="shared" si="5"/>
+        <v>76205.903240679472</v>
+      </c>
+      <c r="BE30">
+        <f t="shared" si="5"/>
+        <v>186114.64558548405</v>
+      </c>
+      <c r="BF30">
+        <f t="shared" si="5"/>
+        <v>1326078.0974784768</v>
+      </c>
+      <c r="BG30">
+        <f t="shared" si="5"/>
+        <v>1414874.6543926725</v>
+      </c>
+    </row>
+    <row r="31" spans="1:59" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>3855</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="4"/>
+        <v>576476.85377447633</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="5"/>
+        <v>297368.44212018262</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <f t="shared" si="5"/>
+        <v>64507.45246373766</v>
+      </c>
+      <c r="BE31">
+        <f t="shared" si="5"/>
+        <v>83908.214348712936</v>
+      </c>
+      <c r="BF31">
+        <f t="shared" si="5"/>
+        <v>119133.44203622997</v>
+      </c>
+      <c r="BG31">
+        <f t="shared" si="5"/>
+        <v>105434.13760257643</v>
+      </c>
+    </row>
+    <row r="33" spans="2:59" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="2">
+        <f>SUM(C25:C31)/1000000</f>
+        <v>5.296512898860291</v>
+      </c>
+      <c r="D33" s="2">
+        <f>SUM(D25:D31)/1000000</f>
+        <v>0.89940475999523439</v>
+      </c>
+      <c r="E33" s="2">
+        <f>SUM(E25:E31)/1000000</f>
+        <v>1.0278727113101764</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" ref="F33:BG33" si="6">SUM(F25:F31)/1000000</f>
+        <v>1.0299693657674367</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.88299490824718518</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.2760990427504577</v>
+      </c>
+      <c r="I33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.3027766337843723</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.1339437804031034</v>
+      </c>
+      <c r="K33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.6893071574976668</v>
+      </c>
+      <c r="L33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.66695080483979996</v>
+      </c>
+      <c r="M33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.47070257225200585</v>
+      </c>
+      <c r="N33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.90192184766723704</v>
+      </c>
+      <c r="O33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.72272984791515527</v>
+      </c>
+      <c r="P33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.86773371087661211</v>
+      </c>
+      <c r="Q33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.1600984848162623</v>
+      </c>
+      <c r="R33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.93141604671355505</v>
+      </c>
+      <c r="S33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.90340111029673575</v>
+      </c>
+      <c r="T33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.2893342586257566</v>
+      </c>
+      <c r="U33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.5167862471396711</v>
+      </c>
+      <c r="V33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.1248031248642483</v>
+      </c>
+      <c r="W33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.5754344452091957</v>
+      </c>
+      <c r="X33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.2858483167139889</v>
+      </c>
+      <c r="Y33" s="2">
+        <f t="shared" si="6"/>
+        <v>3.1016400546475866</v>
+      </c>
+      <c r="Z33" s="2">
+        <f t="shared" si="6"/>
+        <v>3.9059365739143002</v>
+      </c>
+      <c r="AA33" s="2">
+        <f t="shared" si="6"/>
+        <v>4.329993853674976</v>
+      </c>
+      <c r="AB33" s="2">
+        <f t="shared" si="6"/>
+        <v>3.8751535372506192</v>
+      </c>
+      <c r="AC33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.5589709304821864</v>
+      </c>
+      <c r="AD33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.471866057620334</v>
+      </c>
+      <c r="AE33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4986410967463444</v>
+      </c>
+      <c r="AF33" s="2">
+        <f t="shared" si="6"/>
+        <v>0.79330927691501707</v>
+      </c>
+      <c r="AG33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4089486168208001</v>
+      </c>
+      <c r="AH33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4145230556220139</v>
+      </c>
+      <c r="AI33" s="2">
+        <f t="shared" si="6"/>
+        <v>4.3337703754103352</v>
+      </c>
+      <c r="AJ33" s="2">
+        <f t="shared" si="6"/>
+        <v>4.9714454944771393</v>
+      </c>
+      <c r="AK33" s="2">
+        <f t="shared" si="6"/>
+        <v>4.8406883054383565</v>
+      </c>
+      <c r="AL33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.3758363496149659</v>
+      </c>
+      <c r="AM33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.5732344721802876</v>
+      </c>
+      <c r="AN33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.0462829278647221</v>
+      </c>
+      <c r="AO33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.5768403831314102</v>
+      </c>
+      <c r="AP33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.3105700807656917</v>
+      </c>
+      <c r="AQ33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.5067509105961365</v>
+      </c>
+      <c r="AR33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4897379999697071</v>
+      </c>
+      <c r="AS33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.7937356165898906</v>
+      </c>
+      <c r="AT33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.3254454032294181</v>
+      </c>
+      <c r="AU33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AV33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AX33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC33" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0232296871222231</v>
+      </c>
+      <c r="BE33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0333216786502921</v>
+      </c>
+      <c r="BF33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.4664556269819577</v>
+      </c>
+      <c r="BG33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.3203115781625523</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>